--- a/outputs/question1/result1.xlsx
+++ b/outputs/question1/result1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="R18e17c5348c6468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="Rcf0438b7a02f4c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="R44f822c197fd40fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="R4c7355ad9d0c4f04"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -791,7 +791,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:v>1406.6410999999998</x:v>
+        <x:v>1103.3862663097989</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="14" customHeight="1">
@@ -799,7 +799,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="7" t="n">
-        <x:v>1406.3298666666665</x:v>
+        <x:v>1103.0750329764658</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="14" customHeight="1">
@@ -807,7 +807,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B4" s="7" t="n">
-        <x:v>1407.38385</x:v>
+        <x:v>1104.1290163097992</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="14" customHeight="1">
@@ -815,7 +815,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="7" t="n">
-        <x:v>1409.07395</x:v>
+        <x:v>1105.819116309799</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="14" customHeight="1">
@@ -823,7 +823,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="7" t="n">
-        <x:v>1409.8045499999998</x:v>
+        <x:v>1106.549716309799</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="14" customHeight="1">
@@ -831,7 +831,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="7" t="n">
-        <x:v>576.6400166666666</x:v>
+        <x:v>1106.718516309799</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="14" customHeight="1">
@@ -839,7 +839,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="7" t="n">
-        <x:v>577.8597</x:v>
+        <x:v>1107.9381996431325</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="14" customHeight="1">
@@ -847,7 +847,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="7" t="n">
-        <x:v>577.9938666666667</x:v>
+        <x:v>1108.0723663097992</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="14" customHeight="1">
@@ -855,7 +855,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="7" t="n">
-        <x:v>911.1613833333333</x:v>
+        <x:v>1107.9065496431324</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="14" customHeight="1">
@@ -863,7 +863,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="7" t="n">
-        <x:v>580.41545</x:v>
+        <x:v>971.0721591362851</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="14" customHeight="1">
@@ -871,7 +871,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B12" s="7" t="n">
-        <x:v>582.5140166666666</x:v>
+        <x:v>639.8373924696185</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="14" customHeight="1">
@@ -879,7 +879,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="7" t="n">
-        <x:v>583.0740499999999</x:v>
+        <x:v>640.3974258029518</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="14" customHeight="1">
@@ -887,7 +887,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B14" s="7" t="n">
-        <x:v>584.2049166666666</x:v>
+        <x:v>641.5282924696185</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="14" customHeight="1">
@@ -1055,7 +1055,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B35" s="7" t="n">
-        <x:v>1383.659783333333</x:v>
+        <x:v>548.739236975584</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="14" customHeight="1">
@@ -1063,7 +1063,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B36" s="7" t="n">
-        <x:v>591.1401999999999</x:v>
+        <x:v>256.21965364225076</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="14" customHeight="1">
@@ -1071,7 +1071,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B37" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.0000036422507037059404</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="14" customHeight="1">
@@ -1151,7 +1151,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B47" s="7" t="n">
-        <x:v>0.0000354247444982776</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="14" customHeight="1">
@@ -1319,7 +1319,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B68" s="7" t="n">
-        <x:v>575.1709166666665</x:v>
+        <x:v>176.20015949516568</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="14" customHeight="1">
@@ -1327,7 +1327,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B69" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>161.73104282849926</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="14" customHeight="1">
@@ -1335,7 +1335,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B70" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>483.3749261618325</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="14" customHeight="1">
@@ -1343,7 +1343,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B71" s="7" t="n">
-        <x:v>179.27712766492994</x:v>
+        <x:v>544.0318666666665</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="14" customHeight="1">
@@ -1391,7 +1391,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B77" s="7" t="n">
-        <x:v>498.27073333333317</x:v>
+        <x:v>302.82249999999965</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="14" customHeight="1">
@@ -1503,7 +1503,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B91" s="7" t="n">
-        <x:v>112.0898666666667</x:v>
+        <x:v>168.32528847736623</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="14" customHeight="1">
@@ -1511,7 +1511,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B92" s="7" t="n">
-        <x:v>266.73269362139905</x:v>
+        <x:v>210.49727181069952</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="14" customHeight="1">
@@ -1655,7 +1655,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B110" s="7" t="n">
-        <x:v>531.8940499999999</x:v>
+        <x:v>641.1612999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="14" customHeight="1">
@@ -1679,7 +1679,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B113" s="7" t="n">
-        <x:v>696.5043833333333</x:v>
+        <x:v>598.3937750000001</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="14" customHeight="1">
@@ -1687,7 +1687,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B114" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>273.19032500000014</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="14" customHeight="1">
@@ -1775,7 +1775,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B125" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>48.98636666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="14" customHeight="1">
@@ -1783,7 +1783,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B126" s="7" t="n">
-        <x:v>715.8689166666666</x:v>
+        <x:v>382.53558333333325</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="14" customHeight="1">
@@ -1839,7 +1839,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B133" s="7" t="n">
-        <x:v>1393.7903166666665</x:v>
+        <x:v>893.7903166666665</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="14" customHeight="1">
@@ -1847,7 +1847,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B134" s="7" t="n">
-        <x:v>1384.8989</x:v>
+        <x:v>1218.2322333333332</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="14" customHeight="1">
@@ -1855,7 +1855,7 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B135" s="7" t="n">
-        <x:v>568.8260499999999</x:v>
+        <x:v>962.7654439393937</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="14" customHeight="1">
@@ -1863,7 +1863,7 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B136" s="7" t="n">
-        <x:v>1396.98855</x:v>
+        <x:v>957.5946106060604</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="14" customHeight="1">
@@ -1871,7 +1871,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B137" s="7" t="n">
-        <x:v>1397.7598666666665</x:v>
+        <x:v>958.365927272727</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="14" customHeight="1">
@@ -1879,7 +1879,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B138" s="7" t="n">
-        <x:v>566.7474333333332</x:v>
+        <x:v>960.686827272727</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="14" customHeight="1">
@@ -1887,7 +1887,7 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B139" s="7" t="n">
-        <x:v>1399.8737666666666</x:v>
+        <x:v>960.4798272727273</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="14" customHeight="1">
@@ -1895,7 +1895,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B140" s="7" t="n">
-        <x:v>567.83015</x:v>
+        <x:v>961.769543939394</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="14" customHeight="1">
@@ -1903,7 +1903,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B141" s="7" t="n">
-        <x:v>569.3586333333333</x:v>
+        <x:v>963.2980272727273</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="14" customHeight="1">
@@ -1911,7 +1911,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B142" s="7" t="n">
-        <x:v>1403.6635166666665</x:v>
+        <x:v>964.2695772727272</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="14" customHeight="1">
@@ -1919,7 +1919,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B143" s="7" t="n">
-        <x:v>904.9487166666667</x:v>
+        <x:v>965.5547772727273</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="14" customHeight="1">
@@ -1927,7 +1927,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B144" s="7" t="n">
-        <x:v>573.1768333333333</x:v>
+        <x:v>967.1162272727273</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="14" customHeight="1">
@@ -1935,7 +1935,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B145" s="7" t="n">
-        <x:v>574.1209833333332</x:v>
+        <x:v>968.0603772727272</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1973,7 +1973,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B2" s="8" t="n">
-        <x:v>4500</x:v>
+        <x:v>5727.272727272727</x:v>
       </x:c>
       <x:c r="C2" s="8" t="n">
         <x:v>0</x:v>
@@ -1990,10 +1990,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B3" s="8" t="n">
-        <x:v>833.3333333333333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" s="8" t="n">
-        <x:v>5947.419714575255</x:v>
+        <x:v>6283.9275057399145</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
         <x:v>153</x:v>
@@ -2007,7 +2007,7 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B4" s="8" t="n">
-        <x:v>3954.6309109982626</x:v>
+        <x:v>4565.52086181883</x:v>
       </x:c>
       <x:c r="C4" s="8" t="n">
         <x:v>2121.4184333333333</x:v>
@@ -2018,7 +2018,7 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B5" s="8" t="n">
-        <x:v>6119.3685102880645</x:v>
+        <x:v>5923.920276954731</x:v>
       </x:c>
       <x:c r="C5" s="8" t="n">
         <x:v>91.1013833333335</x:v>
@@ -2032,7 +2032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="8" t="n">
-        <x:v>5068.68685</x:v>
+        <x:v>4784.339883333333</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="5" customFormat="1" ht="14" customHeight="1">
@@ -2040,10 +2040,10 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B7" s="8" t="n">
-        <x:v>5333.333333333333</x:v>
+        <x:v>4939.393939393939</x:v>
       </x:c>
       <x:c r="C7" s="8" t="n">
-        <x:v>3571.31315</x:v>
+        <x:v>3855.6601166666665</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/question1/result1.xlsx
+++ b/outputs/question1/result1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="R44f822c197fd40fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="R4c7355ad9d0c4f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="R769a7af0b89c4e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="R697896a62aaa40e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -791,7 +791,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:v>1103.3862663097989</x:v>
+        <x:v>1406.3298666666665</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="14" customHeight="1">
@@ -799,7 +799,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="7" t="n">
-        <x:v>1103.0750329764658</x:v>
+        <x:v>1407.38385</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="14" customHeight="1">
@@ -807,7 +807,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B4" s="7" t="n">
-        <x:v>1104.1290163097992</x:v>
+        <x:v>1409.07395</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="14" customHeight="1">
@@ -815,7 +815,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="7" t="n">
-        <x:v>1105.819116309799</x:v>
+        <x:v>1409.8045499999998</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="14" customHeight="1">
@@ -823,7 +823,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="7" t="n">
-        <x:v>1106.549716309799</x:v>
+        <x:v>1409.9733499999998</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="14" customHeight="1">
@@ -831,7 +831,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="7" t="n">
-        <x:v>1106.718516309799</x:v>
+        <x:v>577.8597</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="14" customHeight="1">
@@ -839,7 +839,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="7" t="n">
-        <x:v>1107.9381996431325</x:v>
+        <x:v>577.9938666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="14" customHeight="1">
@@ -847,7 +847,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="7" t="n">
-        <x:v>1108.0723663097992</x:v>
+        <x:v>577.82805</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="14" customHeight="1">
@@ -855,7 +855,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="7" t="n">
-        <x:v>1107.9065496431324</x:v>
+        <x:v>580.41545</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="14" customHeight="1">
@@ -863,7 +863,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="7" t="n">
-        <x:v>971.0721591362851</x:v>
+        <x:v>582.5140166666666</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="14" customHeight="1">
@@ -871,7 +871,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B12" s="7" t="n">
-        <x:v>639.8373924696185</x:v>
+        <x:v>583.0740499999999</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="14" customHeight="1">
@@ -879,7 +879,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="7" t="n">
-        <x:v>640.3974258029518</x:v>
+        <x:v>584.2049166666666</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="14" customHeight="1">
@@ -887,7 +887,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B14" s="7" t="n">
-        <x:v>641.5282924696185</x:v>
+        <x:v>585.4397833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="14" customHeight="1">
@@ -895,7 +895,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="7" t="n">
-        <x:v>585.4397833333333</x:v>
+        <x:v>586.1447499999999</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="14" customHeight="1">
@@ -903,7 +903,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="7" t="n">
-        <x:v>586.1447499999999</x:v>
+        <x:v>586.3207666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="14" customHeight="1">
@@ -911,7 +911,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="7" t="n">
-        <x:v>586.3207666666666</x:v>
+        <x:v>586.4253</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="14" customHeight="1">
@@ -919,7 +919,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="7" t="n">
-        <x:v>586.4253</x:v>
+        <x:v>586.8496</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="14" customHeight="1">
@@ -927,7 +927,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="7" t="n">
-        <x:v>586.8496</x:v>
+        <x:v>587.8210166666667</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="14" customHeight="1">
@@ -935,7 +935,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B20" s="7" t="n">
-        <x:v>587.8210166666667</x:v>
+        <x:v>589.5475666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="14" customHeight="1">
@@ -943,7 +943,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="7" t="n">
-        <x:v>589.5475666666666</x:v>
+        <x:v>590.8134666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="14" customHeight="1">
@@ -951,7 +951,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="7" t="n">
-        <x:v>590.8134666666666</x:v>
+        <x:v>590.2131166666666</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="14" customHeight="1">
@@ -959,7 +959,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B23" s="7" t="n">
-        <x:v>590.2131166666666</x:v>
+        <x:v>591.0662666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="14" customHeight="1">
@@ -967,7 +967,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B24" s="7" t="n">
-        <x:v>591.0662666666666</x:v>
+        <x:v>593.3678333333332</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="14" customHeight="1">
@@ -975,7 +975,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="7" t="n">
-        <x:v>593.3678333333332</x:v>
+        <x:v>593.6596833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="14" customHeight="1">
@@ -983,7 +983,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B26" s="7" t="n">
-        <x:v>593.6596833333333</x:v>
+        <x:v>592.7863833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="14" customHeight="1">
@@ -991,7 +991,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="7" t="n">
-        <x:v>592.7863833333333</x:v>
+        <x:v>593.3378666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="14" customHeight="1">
@@ -999,7 +999,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B28" s="7" t="n">
-        <x:v>593.3378666666666</x:v>
+        <x:v>596.6757666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="14" customHeight="1">
@@ -1007,7 +1007,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B29" s="7" t="n">
-        <x:v>596.6757666666666</x:v>
+        <x:v>597.78025</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="14" customHeight="1">
@@ -1015,7 +1015,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B30" s="7" t="n">
-        <x:v>597.78025</x:v>
+        <x:v>595.1624999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="14" customHeight="1">
@@ -1023,7 +1023,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B31" s="7" t="n">
-        <x:v>595.1624999999999</x:v>
+        <x:v>590.6065</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="14" customHeight="1">
@@ -1031,7 +1031,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B32" s="7" t="n">
-        <x:v>590.6065</x:v>
+        <x:v>589.4851833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="14" customHeight="1">
@@ -1039,7 +1039,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="7" t="n">
-        <x:v>589.4851833333333</x:v>
+        <x:v>578.4554499999999</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="14" customHeight="1">
@@ -1047,7 +1047,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B34" s="7" t="n">
-        <x:v>578.4554499999999</x:v>
+        <x:v>550.3264499999999</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="14" customHeight="1">
@@ -1055,7 +1055,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B35" s="7" t="n">
-        <x:v>548.739236975584</x:v>
+        <x:v>1424.4735333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="14" customHeight="1">
@@ -1063,7 +1063,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B36" s="7" t="n">
-        <x:v>256.21965364225076</x:v>
+        <x:v>668.2538833333332</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="14" customHeight="1">
@@ -1071,7 +1071,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B37" s="7" t="n">
-        <x:v>0.0000036422507037059404</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="14" customHeight="1">
@@ -1151,7 +1151,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B47" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.000030823864284047874</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="14" customHeight="1">
@@ -1319,7 +1319,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B68" s="7" t="n">
-        <x:v>176.20015949516568</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="14" customHeight="1">
@@ -1327,7 +1327,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B69" s="7" t="n">
-        <x:v>161.73104282849926</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="14" customHeight="1">
@@ -1335,7 +1335,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B70" s="7" t="n">
-        <x:v>483.3749261618325</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="14" customHeight="1">
@@ -1343,7 +1343,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B71" s="7" t="n">
-        <x:v>544.0318666666665</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="14" customHeight="1">
@@ -1351,7 +1351,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B72" s="7" t="n">
-        <x:v>520.1245166666665</x:v>
+        <x:v>407.18910577301364</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="14" customHeight="1">
@@ -1359,7 +1359,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B73" s="7" t="n">
-        <x:v>486.40289999999993</x:v>
+        <x:v>480.4124499999999</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="14" customHeight="1">
@@ -1367,7 +1367,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B74" s="7" t="n">
-        <x:v>480.4124499999999</x:v>
+        <x:v>485.29999999999995</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="14" customHeight="1">
@@ -1375,7 +1375,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B75" s="7" t="n">
-        <x:v>485.29999999999995</x:v>
+        <x:v>488.6069666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="14" customHeight="1">
@@ -1383,7 +1383,7 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B76" s="7" t="n">
-        <x:v>488.6069666666666</x:v>
+        <x:v>498.27073333333317</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="14" customHeight="1">
@@ -1391,7 +1391,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B77" s="7" t="n">
-        <x:v>302.82249999999965</x:v>
+        <x:v>528.7815666666668</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="14" customHeight="1">
@@ -1503,7 +1503,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B91" s="7" t="n">
-        <x:v>168.32528847736623</x:v>
+        <x:v>154.26184999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="14" customHeight="1">
@@ -1511,7 +1511,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B92" s="7" t="n">
-        <x:v>210.49727181069952</x:v>
+        <x:v>448.3769117283957</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="14" customHeight="1">
@@ -1519,7 +1519,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B93" s="7" t="n">
-        <x:v>197.52351666666664</x:v>
+        <x:v>244.8140333333332</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="14" customHeight="1">
@@ -1527,7 +1527,7 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B94" s="7" t="n">
-        <x:v>244.8140333333332</x:v>
+        <x:v>295.5346166666667</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="14" customHeight="1">
@@ -1535,7 +1535,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B95" s="7" t="n">
-        <x:v>295.5346166666667</x:v>
+        <x:v>345.77750000000015</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="14" customHeight="1">
@@ -1543,7 +1543,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B96" s="7" t="n">
-        <x:v>345.77750000000015</x:v>
+        <x:v>394.9314833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="14" customHeight="1">
@@ -1551,7 +1551,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B97" s="7" t="n">
-        <x:v>394.9314833333333</x:v>
+        <x:v>445.4316500000001</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="14" customHeight="1">
@@ -1559,7 +1559,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B98" s="7" t="n">
-        <x:v>445.4316500000001</x:v>
+        <x:v>495.69658333333325</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="14" customHeight="1">
@@ -1567,7 +1567,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B99" s="7" t="n">
-        <x:v>495.69658333333325</x:v>
+        <x:v>547.11905</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="14" customHeight="1">
@@ -1575,7 +1575,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B100" s="7" t="n">
-        <x:v>547.11905</x:v>
+        <x:v>599.9854333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="14" customHeight="1">
@@ -1583,7 +1583,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B101" s="7" t="n">
-        <x:v>599.9854333333333</x:v>
+        <x:v>635.4297499999999</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="14" customHeight="1">
@@ -1591,7 +1591,7 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B102" s="7" t="n">
-        <x:v>635.4297499999999</x:v>
+        <x:v>660.8306833333334</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="14" customHeight="1">
@@ -1599,7 +1599,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B103" s="7" t="n">
-        <x:v>660.8306833333334</x:v>
+        <x:v>702.0369333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="14" customHeight="1">
@@ -1607,7 +1607,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B104" s="7" t="n">
-        <x:v>702.0369333333333</x:v>
+        <x:v>738.0657833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="14" customHeight="1">
@@ -1615,7 +1615,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B105" s="7" t="n">
-        <x:v>738.0657833333333</x:v>
+        <x:v>775.9447166666666</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="14" customHeight="1">
@@ -1623,7 +1623,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B106" s="7" t="n">
-        <x:v>775.9447166666666</x:v>
+        <x:v>826.08325</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="14" customHeight="1">
@@ -1631,7 +1631,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B107" s="7" t="n">
-        <x:v>826.08325</x:v>
+        <x:v>762.4227999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="14" customHeight="1">
@@ -1639,7 +1639,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B108" s="7" t="n">
-        <x:v>762.4227999999999</x:v>
+        <x:v>636.9826166666667</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="14" customHeight="1">
@@ -1647,7 +1647,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B109" s="7" t="n">
-        <x:v>636.9826166666667</x:v>
+        <x:v>641.1612999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="14" customHeight="1">
@@ -1655,7 +1655,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B110" s="7" t="n">
-        <x:v>641.1612999999999</x:v>
+        <x:v>580.7979333333344</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="14" customHeight="1">
@@ -1663,7 +1663,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B111" s="7" t="n">
-        <x:v>678.8305333333333</x:v>
+        <x:v>686.2684999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="14" customHeight="1">
@@ -1671,7 +1671,7 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B112" s="7" t="n">
-        <x:v>686.2684999999999</x:v>
+        <x:v>696.5043833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="14" customHeight="1">
@@ -1679,7 +1679,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B113" s="7" t="n">
-        <x:v>598.3937750000001</x:v>
+        <x:v>704.6342666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="14" customHeight="1">
@@ -1687,7 +1687,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B114" s="7" t="n">
-        <x:v>273.19032500000014</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="14" customHeight="1">
@@ -1775,7 +1775,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B125" s="7" t="n">
-        <x:v>48.98636666666664</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="14" customHeight="1">
@@ -1783,7 +1783,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B126" s="7" t="n">
-        <x:v>382.53558333333325</x:v>
+        <x:v>717.0051166666667</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="14" customHeight="1">
@@ -1791,7 +1791,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B127" s="7" t="n">
-        <x:v>717.0051166666667</x:v>
+        <x:v>720.1603</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="14" customHeight="1">
@@ -1799,7 +1799,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B128" s="7" t="n">
-        <x:v>720.1603</x:v>
+        <x:v>717.0548666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="14" customHeight="1">
@@ -1807,7 +1807,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B129" s="7" t="n">
-        <x:v>717.0548666666666</x:v>
+        <x:v>720.4459666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="14" customHeight="1">
@@ -1815,7 +1815,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B130" s="7" t="n">
-        <x:v>720.4459666666667</x:v>
+        <x:v>738.1347166666666</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="14" customHeight="1">
@@ -1823,7 +1823,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B131" s="7" t="n">
-        <x:v>738.1347166666666</x:v>
+        <x:v>671.6935666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="14" customHeight="1">
@@ -1831,7 +1831,7 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B132" s="7" t="n">
-        <x:v>671.6935666666666</x:v>
+        <x:v>560.4569833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="14" customHeight="1">
@@ -1839,7 +1839,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B133" s="7" t="n">
-        <x:v>893.7903166666665</x:v>
+        <x:v>1384.8989</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="14" customHeight="1">
@@ -1847,7 +1847,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B134" s="7" t="n">
-        <x:v>1218.2322333333332</x:v>
+        <x:v>1402.1593833333332</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="14" customHeight="1">
@@ -1855,7 +1855,7 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B135" s="7" t="n">
-        <x:v>962.7654439393937</x:v>
+        <x:v>563.6552166666667</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="14" customHeight="1">
@@ -1863,7 +1863,7 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B136" s="7" t="n">
-        <x:v>957.5946106060604</x:v>
+        <x:v>1397.7598666666665</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="14" customHeight="1">
@@ -1871,7 +1871,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B137" s="7" t="n">
-        <x:v>958.365927272727</x:v>
+        <x:v>1400.0807666666665</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="14" customHeight="1">
@@ -1879,7 +1879,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B138" s="7" t="n">
-        <x:v>960.686827272727</x:v>
+        <x:v>566.5404333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="14" customHeight="1">
@@ -1887,7 +1887,7 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B139" s="7" t="n">
-        <x:v>960.4798272727273</x:v>
+        <x:v>1401.1634833333333</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="14" customHeight="1">
@@ -1895,7 +1895,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B140" s="7" t="n">
-        <x:v>961.769543939394</x:v>
+        <x:v>569.3586333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="14" customHeight="1">
@@ -1903,7 +1903,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B141" s="7" t="n">
-        <x:v>963.2980272727273</x:v>
+        <x:v>903.6635166666666</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="14" customHeight="1">
@@ -1911,7 +1911,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B142" s="7" t="n">
-        <x:v>964.2695772727272</x:v>
+        <x:v>1404.9487166666665</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="14" customHeight="1">
@@ -1919,7 +1919,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B143" s="7" t="n">
-        <x:v>965.5547772727273</x:v>
+        <x:v>573.1768333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="14" customHeight="1">
@@ -1927,7 +1927,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B144" s="7" t="n">
-        <x:v>967.1162272727273</x:v>
+        <x:v>574.1209833333332</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="14" customHeight="1">
@@ -1935,7 +1935,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B145" s="7" t="n">
-        <x:v>968.0603772727272</x:v>
+        <x:v>906.6410999999999</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1973,7 +1973,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B2" s="8" t="n">
-        <x:v>5727.272727272727</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="C2" s="8" t="n">
         <x:v>0</x:v>
@@ -1990,10 +1990,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B3" s="8" t="n">
-        <x:v>0</x:v>
+        <x:v>833.3333333333333</x:v>
       </x:c>
       <x:c r="C3" s="8" t="n">
-        <x:v>6283.9275057399145</x:v>
+        <x:v>5697.587285842802</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
         <x:v>153</x:v>
@@ -2007,10 +2007,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B4" s="8" t="n">
-        <x:v>4565.52086181883</x:v>
+        <x:v>3434.177889106347</x:v>
       </x:c>
       <x:c r="C4" s="8" t="n">
-        <x:v>2121.4184333333333</x:v>
+        <x:v>1702.9969833333334</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="5" customFormat="1" ht="14" customHeight="1">
@@ -2018,10 +2018,10 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B5" s="8" t="n">
-        <x:v>5923.920276954731</x:v>
+        <x:v>5953.199295061729</x:v>
       </x:c>
       <x:c r="C5" s="8" t="n">
-        <x:v>91.1013833333335</x:v>
+        <x:v>203.1912500000002</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="5" customFormat="1" ht="14" customHeight="1">
@@ -2032,7 +2032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="8" t="n">
-        <x:v>4784.339883333333</x:v>
+        <x:v>5064.262966666665</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="5" customFormat="1" ht="14" customHeight="1">
@@ -2040,10 +2040,10 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B7" s="8" t="n">
-        <x:v>4939.393939393939</x:v>
+        <x:v>5333.333333333333</x:v>
       </x:c>
       <x:c r="C7" s="8" t="n">
-        <x:v>3855.6601166666665</x:v>
+        <x:v>3575.737033333333</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
